--- a/Diagramme.xlsx
+++ b/Diagramme.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b51156f9d0f1fed/Desktop/G22b 24_25/Maturaarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="589" documentId="11_AD4DB114E441178AC67DF42366D6E2A0683EDF1B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2DC9214-1BEB-4E4F-9D30-0DC687D07FDE}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{755D1C1C-67F1-4617-8DE7-E8571A5A2B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{430ECF36-165E-4976-901E-EC6FA8A428C5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -145,7 +156,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -163,7 +174,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -273,6 +284,51 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="de-DE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>Tabelle1!$A$3:$A$16</c:f>
@@ -567,6 +623,51 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="de-DE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>Tabelle1!$A$3:$A$16</c:f>
@@ -915,6 +1016,7 @@
         <c:axId val="363675023"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="100000000"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -940,9 +1042,7 @@
         <c:spPr>
           <a:noFill/>
           <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1056,7 +1156,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1166,6 +1266,92 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:name>Trendlinie</c:name>
+            <c:spPr>
+              <a:ln w="31750" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.9604912566126411E-2"/>
+                  <c:y val="0.13903211130562601"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>y = 1.404x + 456.33</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="de-DE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>Tabelle1!$A$20:$A$33</c:f>
@@ -1800,7 +1986,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2490,6 +2676,1828 @@
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000000-3076-4D89-B1A6-8F939E0093C3}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="470449615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="470450575"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="470450575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="470449615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-CH"/>
+              <a:t>Distanzberechnungen</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>QuerySquare</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Tabelle1!$A$3:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$C$3:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>79027</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>145623</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>232220</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>439237</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>535398</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>673617</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>823559</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1310498</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1389327</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1908755</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2651870</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3339681</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3929426</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4711659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5E37-43B7-AD17-5B9F80E77B96}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>QueryCircle</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Tabelle1!$A$3:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$D$3:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>84508</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138808</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>235269</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>335356</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>461456</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>622943</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>745910</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>960018</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1331038</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1654997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2419180</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2817189</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3679637</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4467624</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5E37-43B7-AD17-5B9F80E77B96}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="363671663"/>
+        <c:axId val="363675023"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Partikelanzahl</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$3:$A$16</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3500</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4500</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$3:$A$16</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3500</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4500</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-5E37-43B7-AD17-5B9F80E77B96}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$B$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Naive</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$3:$A$16</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3500</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4500</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$B$3:$B$16</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>999000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2248500</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3998000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>6247500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8997000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>12246500</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>15996000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>20245500</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>24995000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>35994000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>48993000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>63992000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>80991000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>99990000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-5E37-43B7-AD17-5B9F80E77B96}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="363671663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="363675023"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="363675023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="5000000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="363671663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-CH"/>
+              <a:t>Durchschnittliche Zeit pro Frame [ms]</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$C$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>QuerySquare</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Tabelle1!$A$37:$A$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$C$37:$C$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>412</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>534</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5EC8-481A-81B6-B34898CDBC44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$D$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>QueryCircle</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Tabelle1!$A$37:$A$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$D$37:$D$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>387</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>502</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5EC8-481A-81B6-B34898CDBC44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="470449615"/>
+        <c:axId val="470450575"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Partikelanzahl</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$37:$A$50</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3500</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4500</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$37:$A$50</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3500</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4500</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-5EC8-481A-81B6-B34898CDBC44}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$B$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Naive</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$A$37:$A$50</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3500</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4500</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$B$37:$B$50</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="14"/>
+                      <c:pt idx="0">
+                        <c:v>32</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>74</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>130</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>210</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>303</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>426</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>517</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>677</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>870</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1202</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1728</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2221</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2813</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>3445</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-5EC8-481A-81B6-B34898CDBC44}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -2807,6 +4815,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -3814,6 +5902,1012 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4426,11 +7520,83 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>304599</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>9173</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B46AE130-E795-4792-94AC-063112E602DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>410883</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>168088</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>112897</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>161804</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{963C2A5C-84E0-41C5-A6B1-1CCE7460C9A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4697,7 +7863,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.6328125" customWidth="1"/>
